--- a/output/pdf_financials_xlsx/LIT.xlsx
+++ b/output/pdf_financials_xlsx/LIT.xlsx
@@ -1384,10 +1384,10 @@
         <v>-1.631952</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.751475</v>
+        <v>-0.751475</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>8.491904</v>
+        <v>-8.491904</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-8.483193999999999</v>
@@ -1712,10 +1712,10 @@
         <v>-1.631952</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.751475</v>
+        <v>-0.751475</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8.491904</v>
+        <v>-8.491904</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-8.483193999999999</v>
@@ -1913,10 +1913,10 @@
         <v>-1.631952</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.751475</v>
+        <v>-0.751475</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>8.491904</v>
+        <v>-8.491904</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-8.483193999999999</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-12.686733</v>
+        <v>12.686733</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>18.786875</v>
+        <v>-18.786875</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.870898</v>
+        <v>-18.870898</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.7766</v>
+        <v>-18.7766</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>49.992275</v>
+        <v>-49.992275</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>-84.83194</v>
@@ -2205,10 +2205,10 @@
         <v>-1.631952</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.751475</v>
+        <v>-0.751475</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>8.491904</v>
+        <v>-8.491904</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-8.483193999999999</v>
@@ -2339,10 +2339,10 @@
         <v>-1.631952</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.751773</v>
+        <v>-0.751177</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2369,13 +2369,13 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8.495181000000001</v>
+        <v>-8.488626999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-8.483193999999999</v>
@@ -2503,10 +2503,10 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6456,49 +6456,49 @@
         <v>1.730689</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.94649</v>
+        <v>2.037306</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.219884</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.32709</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.32709</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.32709</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.32709</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.912769</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.503858</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.366824</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.366824</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.256679999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.875161</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.882277</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>14.800474</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>14.800474</v>
       </c>
     </row>
     <row r="93">
@@ -10984,7 +10984,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12604,7 +12608,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13642,7 +13650,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14794,7 +14806,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15758,7 +15774,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16586,7 +16606,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -18822,7 +18846,11 @@
           <t>Reserves 4 2,219,884</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -48827,10 +48855,10 @@
         </is>
       </c>
       <c r="R378" s="5" t="n">
-        <v>1.999691</v>
+        <v>-1.999691</v>
       </c>
       <c r="S378" s="5" t="n">
-        <v>8.483193999999999</v>
+        <v>-8.483193999999999</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -50095,10 +50123,10 @@
         </is>
       </c>
       <c r="P390" s="5" t="n">
-        <v>8.491904</v>
+        <v>-8.491904</v>
       </c>
       <c r="Q390" s="5" t="n">
-        <v>0.375532</v>
+        <v>-0.375532</v>
       </c>
       <c r="R390" t="inlineStr">
         <is>
@@ -51249,13 +51277,13 @@
         </is>
       </c>
       <c r="L401" s="5" t="n">
-        <v>0.044907</v>
+        <v>-0.044907</v>
       </c>
       <c r="M401" s="5" t="n">
-        <v>0.039482</v>
+        <v>-0.039482</v>
       </c>
       <c r="N401" s="5" t="n">
-        <v>0.751475</v>
+        <v>-0.751475</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
@@ -52817,10 +52845,10 @@
         </is>
       </c>
       <c r="H416" s="5" t="n">
-        <v>0.380602</v>
+        <v>-0.380602</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>0.159517</v>
+        <v>-0.159517</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LIT.xlsx
+++ b/output/pdf_financials_xlsx/LIT.xlsx
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.080383</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.01421</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001568</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-4.1e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-8.8e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002047</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1146,25 +1146,25 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016221</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000162</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033134</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.539365</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.068011</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.047181</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.042914</v>
       </c>
     </row>
     <row r="13">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.073797</v>
+        <v>-3.15418</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.472349</v>
+        <v>-3.486559</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.631952</v>
@@ -2208,7 +2208,7 @@
         <v>-0.380602</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.159517</v>
+        <v>-0.157949</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.044907</v>
+        <v>-0.044866</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.039482</v>
+        <v>-0.039394</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.751475</v>
+        <v>-0.749428</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2235,25 +2235,25 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-8.491904</v>
+        <v>-8.475683</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.375532</v>
+        <v>-0.37537</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.999691</v>
+        <v>-1.966557</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-8.483193999999999</v>
+        <v>-9.022558999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-55.998483</v>
+        <v>-57.066494</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-22.010157</v>
+        <v>-22.057338</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-24.760054</v>
+        <v>-24.802968</v>
       </c>
     </row>
     <row r="28">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.073797</v>
+        <v>-3.15418</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.472349</v>
+        <v>-3.486559</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.631952</v>
@@ -2342,7 +2342,7 @@
         <v>-0.380602</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.159517</v>
+        <v>-0.157949</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.044907</v>
+        <v>-0.044866</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.039482</v>
+        <v>-0.039394</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.751177</v>
+        <v>-0.74913</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2369,25 +2369,25 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-8.488626999999999</v>
+        <v>-8.472405999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.375532</v>
+        <v>-0.37537</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.999691</v>
+        <v>-1.966557</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-8.483193999999999</v>
+        <v>-9.022558999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-55.998483</v>
+        <v>-57.066494</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-22.000842</v>
+        <v>-22.048023</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-24.751771</v>
+        <v>-24.794685</v>
       </c>
     </row>
     <row r="30">
@@ -2670,40 +2670,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.024502</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.18628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.18628</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.341524</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.020205</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011223</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003236</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.007362</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.575961</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.883712</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.013093</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.010104</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>6.430771</v>
@@ -2796,40 +2796,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.029502</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0042</v>
+        <v>0.19048</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0042</v>
+        <v>0.19048</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.341524</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.120205</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011223</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003236</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.007362</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.575961</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.883712</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.013093</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.010104</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>6.430771</v>
@@ -3552,40 +3552,40 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.051018</v>
+        <v>0.026516</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.190283</v>
+        <v>0.004003</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.190283</v>
+        <v>0.004003</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.347634</v>
+        <v>0.00611</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.02984</v>
+        <v>0.009634999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.011835</v>
+        <v>0.000612</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004945</v>
+        <v>0.001709</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.007919000000000001</v>
+        <v>0.000557</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.646082</v>
+        <v>0.070121</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.98989</v>
+        <v>0.106178</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.046721</v>
+        <v>0.033628</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.033677</v>
+        <v>0.023573</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.039183</v>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -43606,7 +43606,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -43714,7 +43714,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -45490,7 +45490,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -45598,7 +45598,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -47078,7 +47078,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -48464,7 +48464,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -48572,7 +48572,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -49640,7 +49640,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -49748,7 +49748,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -50812,7 +50812,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -50920,7 +50920,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -51864,7 +51864,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -52716,7 +52716,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -54712,7 +54712,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -56608,7 +56608,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E452" s="5" t="n">
